--- a/apps/snapshot/amazon/ship_cost.xlsx
+++ b/apps/snapshot/amazon/ship_cost.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\apps\snapshot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\apps\snapshot\amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8774CC-461B-4E74-B73F-4D0F4E80919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E54C2F-8D00-4B81-9B28-EC5DB44C0DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
   </bookViews>
   <sheets>
     <sheet name="重量" sheetId="1" r:id="rId1"/>
     <sheet name="サイズ" sheetId="2" r:id="rId2"/>
+    <sheet name="輸入" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>g</t>
     <phoneticPr fontId="1"/>
@@ -58,12 +59,28 @@
     <t>cm</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>FedEco</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FedPrio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DHLExp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>day</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +93,15 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -102,8 +128,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -440,10 +469,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6156BC87-47FA-4C5F-9CD6-E090EE6DF024}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>-1</v>
       </c>
@@ -471,12 +500,12 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>500</v>
       </c>
-      <c r="B3">
-        <v>3094</v>
+      <c r="B3" s="1">
+        <v>3639</v>
       </c>
       <c r="C3">
         <v>2979</v>
@@ -484,13 +513,26 @@
       <c r="D3">
         <v>1010</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E3">
+        <v>25</v>
+      </c>
+      <c r="F3">
+        <v>25</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H25" si="0">E3*F3*G3/5000</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1000</v>
       </c>
-      <c r="B4">
-        <v>3543</v>
+      <c r="B4" s="1">
+        <v>4088</v>
       </c>
       <c r="C4">
         <v>3458</v>
@@ -498,13 +540,26 @@
       <c r="D4">
         <v>1010</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1500</v>
       </c>
-      <c r="B5">
-        <v>3968</v>
+      <c r="B5" s="1">
+        <v>4285</v>
       </c>
       <c r="C5">
         <v>3935</v>
@@ -512,13 +567,26 @@
       <c r="D5">
         <v>1010</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E5">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2000</v>
       </c>
-      <c r="B6">
-        <v>4404</v>
+      <c r="B6" s="1">
+        <v>4666</v>
       </c>
       <c r="C6">
         <v>4383</v>
@@ -526,257 +594,594 @@
       <c r="D6">
         <v>1010</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
+        <v>2500</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5156</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ref="H7" si="1">E7*F7*G7/5000</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8">
         <v>3000</v>
       </c>
-      <c r="B7">
-        <v>5275</v>
-      </c>
-      <c r="C7">
+      <c r="B8" s="1">
+        <v>5944</v>
+      </c>
+      <c r="C8">
         <v>5317</v>
-      </c>
-      <c r="D7">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>4000</v>
-      </c>
-      <c r="B8">
-        <v>6385</v>
-      </c>
-      <c r="C8">
-        <v>6476</v>
       </c>
       <c r="D8">
         <v>1250</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E8">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="B9">
-        <v>7744</v>
+        <v>6385</v>
       </c>
       <c r="C9">
-        <v>7891</v>
+        <v>6476</v>
       </c>
       <c r="D9">
         <v>1250</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
+        <v>5000</v>
+      </c>
+      <c r="B10">
+        <v>7744</v>
+      </c>
+      <c r="C10">
+        <v>7891</v>
+      </c>
+      <c r="D10">
+        <v>1250</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11">
         <v>6000</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>8698</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>8733</v>
-      </c>
-      <c r="D10">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>7000</v>
-      </c>
-      <c r="B11">
-        <v>9359</v>
-      </c>
-      <c r="C11">
-        <v>9407</v>
       </c>
       <c r="D11">
         <v>1540</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="B12">
-        <v>10018</v>
+        <v>9359</v>
       </c>
       <c r="C12">
-        <v>10080</v>
+        <v>9407</v>
       </c>
       <c r="D12">
         <v>1540</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="B13">
-        <v>10677</v>
+        <v>10018</v>
       </c>
       <c r="C13">
-        <v>10752</v>
+        <v>10080</v>
       </c>
       <c r="D13">
         <v>1540</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>16</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="B14">
-        <v>12705</v>
+        <v>10677</v>
       </c>
       <c r="C14">
-        <v>13054</v>
+        <v>10752</v>
       </c>
       <c r="D14">
         <v>1540</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
+        <v>10000</v>
+      </c>
+      <c r="B15">
+        <v>12705</v>
+      </c>
+      <c r="C15">
+        <v>13054</v>
+      </c>
+      <c r="D15">
+        <v>1540</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16">
         <v>11000</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>13469</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>13883</v>
-      </c>
-      <c r="D15">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>12000</v>
-      </c>
-      <c r="B16">
-        <v>14234</v>
-      </c>
-      <c r="C16">
-        <v>14714</v>
       </c>
       <c r="D16">
         <v>1870</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>50</v>
+      </c>
+      <c r="G16">
+        <v>11</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="B17">
-        <v>15529</v>
+        <v>14234</v>
       </c>
       <c r="C17">
-        <v>16263</v>
+        <v>14714</v>
       </c>
       <c r="D17">
         <v>1870</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E17">
+        <v>100</v>
+      </c>
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="B18">
-        <v>16317</v>
+        <v>15529</v>
       </c>
       <c r="C18">
-        <v>17128</v>
+        <v>16263</v>
       </c>
       <c r="D18">
         <v>1870</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E18">
+        <v>100</v>
+      </c>
+      <c r="F18">
+        <v>50</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="B19">
-        <v>17106</v>
+        <v>16317</v>
       </c>
       <c r="C19">
-        <v>17993</v>
+        <v>17128</v>
       </c>
       <c r="D19">
         <v>1870</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E19">
+        <v>100</v>
+      </c>
+      <c r="F19">
+        <v>50</v>
+      </c>
+      <c r="G19">
+        <v>14</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
+        <v>15000</v>
+      </c>
+      <c r="B20">
+        <v>17106</v>
+      </c>
+      <c r="C20">
+        <v>17993</v>
+      </c>
+      <c r="D20">
+        <v>1870</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+      <c r="F20">
+        <v>50</v>
+      </c>
+      <c r="G20">
+        <v>15</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21">
         <v>16000</v>
       </c>
-      <c r="B20">
-        <v>18612</v>
-      </c>
-      <c r="C20">
+      <c r="B21">
+        <v>18916</v>
+      </c>
+      <c r="C21">
         <v>19493</v>
-      </c>
-      <c r="D20">
-        <v>2110</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>17000</v>
-      </c>
-      <c r="B21">
-        <v>19428</v>
-      </c>
-      <c r="C21">
-        <v>20385</v>
       </c>
       <c r="D21">
         <v>2110</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>16</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="B22">
-        <v>20246</v>
+        <v>19428</v>
       </c>
       <c r="C22">
-        <v>21278</v>
+        <v>20385</v>
       </c>
       <c r="D22">
         <v>2110</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E22">
+        <v>100</v>
+      </c>
+      <c r="F22">
+        <v>50</v>
+      </c>
+      <c r="G22">
+        <v>17</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="B23">
-        <v>21063</v>
+        <v>20246</v>
       </c>
       <c r="C23">
-        <v>22170</v>
+        <v>21278</v>
       </c>
       <c r="D23">
         <v>2110</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>50</v>
+      </c>
+      <c r="G23">
+        <v>18</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="B24">
-        <v>21881</v>
+        <v>26722</v>
       </c>
       <c r="C24">
-        <v>23061</v>
+        <v>22170</v>
       </c>
       <c r="D24">
         <v>2110</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
+        <v>50</v>
+      </c>
+      <c r="G24">
+        <v>19</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>20000</v>
+      </c>
+      <c r="B25">
+        <v>27751</v>
+      </c>
+      <c r="C25">
+        <v>23061</v>
+      </c>
+      <c r="D25">
+        <v>2110</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>50</v>
+      </c>
+      <c r="G25">
+        <v>20</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>21000</v>
+      </c>
+      <c r="B26">
+        <v>33174</v>
+      </c>
+      <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>50</v>
+      </c>
+      <c r="G26">
+        <v>21</v>
+      </c>
+      <c r="H26">
+        <f>E26*F26*G26/5000</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>26000</v>
+      </c>
+      <c r="B31">
+        <v>26160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>30000</v>
       </c>
     </row>
   </sheetData>
@@ -858,4 +1263,253 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AECCF68-1EA8-413E-ACA2-CAE5CD1A4920}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>3972</v>
+      </c>
+      <c r="C3">
+        <v>4600</v>
+      </c>
+      <c r="D3">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>200</v>
+      </c>
+      <c r="B4">
+        <v>3972</v>
+      </c>
+      <c r="C4">
+        <v>4600</v>
+      </c>
+      <c r="D4">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>300</v>
+      </c>
+      <c r="B5">
+        <v>3972</v>
+      </c>
+      <c r="C5">
+        <v>4600</v>
+      </c>
+      <c r="D5">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>400</v>
+      </c>
+      <c r="B6">
+        <v>3972</v>
+      </c>
+      <c r="C6">
+        <v>4600</v>
+      </c>
+      <c r="D6">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>500</v>
+      </c>
+      <c r="B7">
+        <v>4490</v>
+      </c>
+      <c r="C7">
+        <v>4757</v>
+      </c>
+      <c r="D7">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>600</v>
+      </c>
+      <c r="B8">
+        <v>4490</v>
+      </c>
+      <c r="C8">
+        <v>4757</v>
+      </c>
+      <c r="D8">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>700</v>
+      </c>
+      <c r="B9">
+        <v>4490</v>
+      </c>
+      <c r="C9">
+        <v>4757</v>
+      </c>
+      <c r="D9">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>800</v>
+      </c>
+      <c r="B10">
+        <v>4490</v>
+      </c>
+      <c r="C10">
+        <v>4757</v>
+      </c>
+      <c r="D10">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>900</v>
+      </c>
+      <c r="B11">
+        <v>4490</v>
+      </c>
+      <c r="C11">
+        <v>4757</v>
+      </c>
+      <c r="D11">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>1000</v>
+      </c>
+      <c r="B12">
+        <v>4487</v>
+      </c>
+      <c r="C12">
+        <v>5284</v>
+      </c>
+      <c r="D12">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>1100</v>
+      </c>
+      <c r="B13">
+        <v>4487</v>
+      </c>
+      <c r="C13">
+        <v>5284</v>
+      </c>
+      <c r="D13">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>1200</v>
+      </c>
+      <c r="B14">
+        <v>4487</v>
+      </c>
+      <c r="C14">
+        <v>5284</v>
+      </c>
+      <c r="D14">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>1300</v>
+      </c>
+      <c r="B15">
+        <v>4487</v>
+      </c>
+      <c r="C15">
+        <v>5284</v>
+      </c>
+      <c r="D15">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>1400</v>
+      </c>
+      <c r="B16">
+        <v>5478</v>
+      </c>
+      <c r="C16">
+        <v>6662</v>
+      </c>
+      <c r="D16">
+        <v>6109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>1500</v>
+      </c>
+      <c r="B17">
+        <v>5478</v>
+      </c>
+      <c r="C17">
+        <v>6662</v>
+      </c>
+      <c r="D17">
+        <v>6109</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/apps/snapshot/amazon/ship_cost.xlsx
+++ b/apps/snapshot/amazon/ship_cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\apps\snapshot\amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303CAEB2-CD43-4736-8374-26270E6A835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A96252-1E85-4B09-8CBB-952FD1DB35FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
   </bookViews>
   <sheets>
     <sheet name="重量" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -142,9 +142,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -642,7 +639,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
+      <c r="A12">
         <v>5500</v>
       </c>
       <c r="B12" s="1">
@@ -754,7 +751,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
+      <c r="A20">
         <v>9500</v>
       </c>
       <c r="B20" s="1">
@@ -838,7 +835,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" s="3">
+      <c r="A26">
         <v>12500</v>
       </c>
       <c r="B26" s="1">
@@ -996,10 +993,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AECCF68-1EA8-413E-ACA2-CAE5CD1A4920}">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="4" width="9" style="4"/>
+    <col min="2" max="4" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -1034,13 +1031,13 @@
       <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>25.01</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>28.96</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>28.72</v>
       </c>
     </row>
@@ -1048,13 +1045,13 @@
       <c r="A4">
         <v>200</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>25.01</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>28.96</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>28.72</v>
       </c>
     </row>
@@ -1062,13 +1059,13 @@
       <c r="A5">
         <v>300</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>25.01</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>28.96</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>28.72</v>
       </c>
     </row>
@@ -1076,13 +1073,13 @@
       <c r="A6">
         <v>400</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>25.01</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>28.96</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>28.72</v>
       </c>
     </row>
@@ -1090,13 +1087,13 @@
       <c r="A7">
         <v>500</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>28.27</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>29.95</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>31.74</v>
       </c>
     </row>
@@ -1104,13 +1101,13 @@
       <c r="A8">
         <v>600</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>28.27</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>29.95</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>31.74</v>
       </c>
     </row>
@@ -1118,13 +1115,13 @@
       <c r="A9">
         <v>700</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>28.27</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>29.95</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>31.74</v>
       </c>
     </row>
@@ -1132,13 +1129,13 @@
       <c r="A10">
         <v>800</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>28.27</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>29.95</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>31.74</v>
       </c>
     </row>
@@ -1146,13 +1143,13 @@
       <c r="A11">
         <v>900</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>28.27</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>29.95</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>31.74</v>
       </c>
     </row>
@@ -1160,13 +1157,13 @@
       <c r="A12">
         <v>1000</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>28.25</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>33.270000000000003</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>31.73</v>
       </c>
     </row>
@@ -1174,13 +1171,13 @@
       <c r="A13">
         <v>1100</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>28.25</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>33.270000000000003</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>31.73</v>
       </c>
     </row>
@@ -1188,13 +1185,13 @@
       <c r="A14">
         <v>1200</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>28.25</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>33.270000000000003</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>31.73</v>
       </c>
     </row>
@@ -1202,13 +1199,13 @@
       <c r="A15">
         <v>1300</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>28.25</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>33.270000000000003</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>31.73</v>
       </c>
     </row>
@@ -1216,13 +1213,13 @@
       <c r="A16">
         <v>1400</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>34.49</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>41.94</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>38.46</v>
       </c>
     </row>
@@ -1230,13 +1227,13 @@
       <c r="A17">
         <v>1500</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>34.49</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>41.94</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>38.46</v>
       </c>
     </row>
@@ -1244,13 +1241,13 @@
       <c r="A18">
         <v>1600</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>34.49</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <v>41.94</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>38.46</v>
       </c>
     </row>
@@ -1258,13 +1255,13 @@
       <c r="A19">
         <v>1700</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>34.49</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="3">
         <v>41.94</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>38.46</v>
       </c>
     </row>
@@ -1272,13 +1269,13 @@
       <c r="A20">
         <v>1800</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>34.49</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>41.94</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>38.46</v>
       </c>
     </row>
@@ -1286,13 +1283,13 @@
       <c r="A21">
         <v>1900</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>34.51</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>51.92</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>38.47</v>
       </c>
     </row>
@@ -1300,13 +1297,13 @@
       <c r="A22">
         <v>2000</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>34.51</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>51.92</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>38.47</v>
       </c>
     </row>
@@ -1314,13 +1311,13 @@
       <c r="A23">
         <v>2100</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>34.51</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>51.92</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>38.47</v>
       </c>
     </row>
@@ -1328,13 +1325,13 @@
       <c r="A24">
         <v>2200</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>34.51</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>51.92</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>38.47</v>
       </c>
     </row>
@@ -1342,13 +1339,13 @@
       <c r="A25">
         <v>2300</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>38.06</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>59.39</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>42.3</v>
       </c>
     </row>
@@ -1356,13 +1353,13 @@
       <c r="A26">
         <v>2400</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>38.06</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>59.39</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>42.3</v>
       </c>
     </row>
@@ -1370,13 +1367,13 @@
       <c r="A27">
         <v>2500</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>38.06</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>59.39</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>42.3</v>
       </c>
     </row>
@@ -1384,13 +1381,13 @@
       <c r="A28">
         <v>2600</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>38.06</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>59.39</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>42.3</v>
       </c>
     </row>
@@ -1398,13 +1395,13 @@
       <c r="A29">
         <v>2700</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="3">
         <v>38.06</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <v>59.39</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>42.3</v>
       </c>
     </row>
@@ -1412,13 +1409,13 @@
       <c r="A30">
         <v>2800</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="3">
         <v>41.97</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <v>64.73</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>46.51</v>
       </c>
     </row>
@@ -1426,13 +1423,13 @@
       <c r="A31">
         <v>2900</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3">
         <v>41.97</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <v>64.73</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>46.51</v>
       </c>
     </row>
@@ -1440,13 +1437,13 @@
       <c r="A32">
         <v>3000</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>41.97</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <v>64.73</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>46.51</v>
       </c>
     </row>
@@ -1454,13 +1451,13 @@
       <c r="A33">
         <v>3100</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="3">
         <v>41.97</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>64.73</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>46.51</v>
       </c>
     </row>
@@ -1468,13 +1465,13 @@
       <c r="A34">
         <v>3200</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>45.87</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>67.38</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>50.72</v>
       </c>
     </row>
@@ -1482,13 +1479,13 @@
       <c r="A35">
         <v>3300</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3">
         <v>45.87</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <v>67.38</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>50.72</v>
       </c>
     </row>
@@ -1496,13 +1493,13 @@
       <c r="A36">
         <v>3400</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3">
         <v>45.87</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>67.38</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>50.72</v>
       </c>
     </row>
@@ -1510,13 +1507,13 @@
       <c r="A37">
         <v>3500</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="3">
         <v>45.87</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <v>67.38</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>50.72</v>
       </c>
     </row>
@@ -1743,6 +1740,356 @@
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>8000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>9100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124">
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125">
+        <v>12300</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A126">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A127">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A128">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129">
+        <v>12700</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A134">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <v>13400</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A137">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A138">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139">
+        <v>13700</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A141">
+        <v>13900</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143">
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144">
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A145">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A146">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <v>14600</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152">
+        <v>15000</v>
       </c>
     </row>
   </sheetData>

--- a/apps/snapshot/amazon/ship_cost.xlsx
+++ b/apps/snapshot/amazon/ship_cost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\apps\snapshot\amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A96252-1E85-4B09-8CBB-952FD1DB35FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6082BD-7988-4CCA-ADCD-ECA4AD51743C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{37774DD7-BA91-41C4-834C-E5C1BD4ABBF7}"/>
   </bookViews>
@@ -1521,575 +1521,1610 @@
       <c r="A38">
         <v>3600</v>
       </c>
+      <c r="B38" s="3">
+        <v>45.87</v>
+      </c>
+      <c r="C38" s="3">
+        <v>67.38</v>
+      </c>
+      <c r="D38" s="3">
+        <v>50.72</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>3700</v>
       </c>
+      <c r="B39" s="3">
+        <v>45.88</v>
+      </c>
+      <c r="C39" s="3">
+        <v>68.72</v>
+      </c>
+      <c r="D39" s="3">
+        <v>50.73</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>3800</v>
       </c>
+      <c r="B40" s="3">
+        <v>45.88</v>
+      </c>
+      <c r="C40" s="3">
+        <v>68.72</v>
+      </c>
+      <c r="D40" s="3">
+        <v>50.73</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>3900</v>
       </c>
+      <c r="B41" s="3">
+        <v>45.88</v>
+      </c>
+      <c r="C41" s="3">
+        <v>68.72</v>
+      </c>
+      <c r="D41" s="3">
+        <v>50.73</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>4000</v>
       </c>
+      <c r="B42" s="3">
+        <v>45.88</v>
+      </c>
+      <c r="C42" s="3">
+        <v>68.72</v>
+      </c>
+      <c r="D42" s="3">
+        <v>50.73</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>4100</v>
       </c>
+      <c r="B43" s="3">
+        <v>47.22</v>
+      </c>
+      <c r="C43" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="D43" s="3">
+        <v>52.18</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>4200</v>
       </c>
+      <c r="B44" s="3">
+        <v>47.22</v>
+      </c>
+      <c r="C44" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="D44" s="3">
+        <v>52.18</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>4300</v>
       </c>
+      <c r="B45" s="3">
+        <v>47.22</v>
+      </c>
+      <c r="C45" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="D45" s="3">
+        <v>52.18</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>4400</v>
       </c>
+      <c r="B46" s="3">
+        <v>47.22</v>
+      </c>
+      <c r="C46" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="D46" s="3">
+        <v>52.18</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>4500</v>
       </c>
+      <c r="B47" s="3">
+        <v>47.22</v>
+      </c>
+      <c r="C47" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="D47" s="3">
+        <v>52.18</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>4600</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B48" s="3">
+        <v>52.19</v>
+      </c>
+      <c r="C48" s="3">
+        <v>74.222999999999999</v>
+      </c>
+      <c r="D48" s="3">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>4700</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B49" s="3">
+        <v>52.19</v>
+      </c>
+      <c r="C49" s="3">
+        <v>74.222999999999999</v>
+      </c>
+      <c r="D49" s="3">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4800</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B50" s="3">
+        <v>52.19</v>
+      </c>
+      <c r="C50" s="3">
+        <v>74.222999999999999</v>
+      </c>
+      <c r="D50" s="3">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>4900</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B51" s="3">
+        <v>52.19</v>
+      </c>
+      <c r="C51" s="3">
+        <v>74.222999999999999</v>
+      </c>
+      <c r="D51" s="3">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5000</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B52" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="C52" s="3">
+        <v>76.12</v>
+      </c>
+      <c r="D52" s="3">
+        <v>60.19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5100</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B53" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="C53" s="3">
+        <v>76.12</v>
+      </c>
+      <c r="D53" s="3">
+        <v>60.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5200</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B54" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="C54" s="3">
+        <v>76.12</v>
+      </c>
+      <c r="D54" s="3">
+        <v>60.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5300</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B55" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="C55" s="3">
+        <v>76.12</v>
+      </c>
+      <c r="D55" s="3">
+        <v>60.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5400</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B56" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="C56" s="3">
+        <v>76.12</v>
+      </c>
+      <c r="D56" s="3">
+        <v>60.19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5500</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B57" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="C57" s="3">
+        <v>90.53</v>
+      </c>
+      <c r="D57" s="3">
+        <v>62.82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>5600</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B58" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="C58" s="3">
+        <v>90.53</v>
+      </c>
+      <c r="D58" s="3">
+        <v>62.82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>5700</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B59" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="C59" s="3">
+        <v>90.53</v>
+      </c>
+      <c r="D59" s="3">
+        <v>62.82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>5800</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B60" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="C60" s="3">
+        <v>90.53</v>
+      </c>
+      <c r="D60" s="3">
+        <v>62.82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>5900</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B61" s="3">
+        <v>59.5</v>
+      </c>
+      <c r="C61" s="3">
+        <v>93.86</v>
+      </c>
+      <c r="D61" s="3">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>6000</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B62" s="3">
+        <v>59.5</v>
+      </c>
+      <c r="C62" s="3">
+        <v>93.86</v>
+      </c>
+      <c r="D62" s="3">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>6100</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B63" s="3">
+        <v>59.5</v>
+      </c>
+      <c r="C63" s="3">
+        <v>93.86</v>
+      </c>
+      <c r="D63" s="3">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>6200</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B64" s="3">
+        <v>59.5</v>
+      </c>
+      <c r="C64" s="3">
+        <v>93.86</v>
+      </c>
+      <c r="D64" s="3">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>6300</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B65" s="3">
+        <v>59.5</v>
+      </c>
+      <c r="C65" s="3">
+        <v>93.86</v>
+      </c>
+      <c r="D65" s="3">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>6400</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B66" s="3">
+        <v>61.98</v>
+      </c>
+      <c r="C66" s="3">
+        <v>99.33</v>
+      </c>
+      <c r="D66" s="3">
+        <v>68.099999999999994</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>6500</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B67" s="3">
+        <v>61.98</v>
+      </c>
+      <c r="C67" s="3">
+        <v>99.33</v>
+      </c>
+      <c r="D67" s="3">
+        <v>68.099999999999994</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>6600</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B68" s="3">
+        <v>61.98</v>
+      </c>
+      <c r="C68" s="3">
+        <v>99.33</v>
+      </c>
+      <c r="D68" s="3">
+        <v>68.099999999999994</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>6700</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B69" s="3">
+        <v>61.98</v>
+      </c>
+      <c r="C69" s="3">
+        <v>99.33</v>
+      </c>
+      <c r="D69" s="3">
+        <v>68.099999999999994</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>6800</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B70" s="3">
+        <v>61.98</v>
+      </c>
+      <c r="C70" s="3">
+        <v>99.33</v>
+      </c>
+      <c r="D70" s="3">
+        <v>68.099999999999994</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>6900</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B71" s="3">
+        <v>66.12</v>
+      </c>
+      <c r="C71" s="3">
+        <v>109.7</v>
+      </c>
+      <c r="D71" s="3">
+        <v>73.849999999999994</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>7000</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B72" s="3">
+        <v>66.12</v>
+      </c>
+      <c r="C72" s="3">
+        <v>109.7</v>
+      </c>
+      <c r="D72" s="3">
+        <v>73.849999999999994</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>7100</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B73" s="3">
+        <v>66.12</v>
+      </c>
+      <c r="C73" s="3">
+        <v>109.7</v>
+      </c>
+      <c r="D73" s="3">
+        <v>73.849999999999994</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>7200</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B74" s="3">
+        <v>66.12</v>
+      </c>
+      <c r="C74" s="3">
+        <v>109.7</v>
+      </c>
+      <c r="D74" s="3">
+        <v>73.849999999999994</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>7300</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B75" s="3">
+        <v>69.430000000000007</v>
+      </c>
+      <c r="C75" s="3">
+        <v>114.03</v>
+      </c>
+      <c r="D75" s="3">
+        <v>76.59</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>7400</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B76" s="3">
+        <v>69.430000000000007</v>
+      </c>
+      <c r="C76" s="3">
+        <v>114.03</v>
+      </c>
+      <c r="D76" s="3">
+        <v>76.59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>7500</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B77" s="3">
+        <v>69.430000000000007</v>
+      </c>
+      <c r="C77" s="3">
+        <v>114.03</v>
+      </c>
+      <c r="D77" s="3">
+        <v>76.59</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>7600</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B78" s="3">
+        <v>69.430000000000007</v>
+      </c>
+      <c r="C78" s="3">
+        <v>114.03</v>
+      </c>
+      <c r="D78" s="3">
+        <v>76.59</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>7700</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B79" s="3">
+        <v>69.430000000000007</v>
+      </c>
+      <c r="C79" s="3">
+        <v>114.03</v>
+      </c>
+      <c r="D79" s="3">
+        <v>76.59</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>7800</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B80" s="3">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="C80" s="3">
+        <v>116.39</v>
+      </c>
+      <c r="D80" s="3">
+        <v>79.34</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>7900</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B81" s="3">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="C81" s="3">
+        <v>116.39</v>
+      </c>
+      <c r="D81" s="3">
+        <v>79.34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>8000</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B82" s="3">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="C82" s="3">
+        <v>116.39</v>
+      </c>
+      <c r="D82" s="3">
+        <v>79.34</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>8100</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B83" s="3">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="C83" s="3">
+        <v>116.39</v>
+      </c>
+      <c r="D83" s="3">
+        <v>79.34</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>8200</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B84" s="3">
+        <v>74.94</v>
+      </c>
+      <c r="C84" s="3">
+        <v>118.7</v>
+      </c>
+      <c r="D84" s="3">
+        <v>82.12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>8300</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B85" s="3">
+        <v>74.94</v>
+      </c>
+      <c r="C85" s="3">
+        <v>118.7</v>
+      </c>
+      <c r="D85" s="3">
+        <v>82.12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>8400</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B86" s="3">
+        <v>74.94</v>
+      </c>
+      <c r="C86" s="3">
+        <v>118.7</v>
+      </c>
+      <c r="D86" s="3">
+        <v>82.12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>8500</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B87" s="3">
+        <v>74.94</v>
+      </c>
+      <c r="C87" s="3">
+        <v>118.7</v>
+      </c>
+      <c r="D87" s="3">
+        <v>82.12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>8600</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B88" s="3">
+        <v>74.94</v>
+      </c>
+      <c r="C88" s="3">
+        <v>118.7</v>
+      </c>
+      <c r="D88" s="3">
+        <v>82.12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>8700</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B89" s="3">
+        <v>77.5</v>
+      </c>
+      <c r="C89" s="3">
+        <v>120.03</v>
+      </c>
+      <c r="D89" s="3">
+        <v>84.86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>8800</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B90" s="3">
+        <v>77.5</v>
+      </c>
+      <c r="C90" s="3">
+        <v>120.03</v>
+      </c>
+      <c r="D90" s="3">
+        <v>84.86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>8900</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B91" s="3">
+        <v>77.5</v>
+      </c>
+      <c r="C91" s="3">
+        <v>120.03</v>
+      </c>
+      <c r="D91" s="3">
+        <v>84.86</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>9000</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B92" s="3">
+        <v>77.5</v>
+      </c>
+      <c r="C92" s="3">
+        <v>120.03</v>
+      </c>
+      <c r="D92" s="3">
+        <v>84.86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>9100</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B93" s="3">
+        <v>82.3</v>
+      </c>
+      <c r="C93" s="3">
+        <v>126.89</v>
+      </c>
+      <c r="D93" s="3">
+        <v>91.26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>9200</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B94" s="3">
+        <v>82.3</v>
+      </c>
+      <c r="C94" s="3">
+        <v>126.89</v>
+      </c>
+      <c r="D94" s="3">
+        <v>91.26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>9300</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B95" s="3">
+        <v>82.3</v>
+      </c>
+      <c r="C95" s="3">
+        <v>126.89</v>
+      </c>
+      <c r="D95" s="3">
+        <v>91.26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>9400</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B96" s="3">
+        <v>82.3</v>
+      </c>
+      <c r="C96" s="3">
+        <v>126.89</v>
+      </c>
+      <c r="D96" s="3">
+        <v>91.26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>9500</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B97" s="3">
+        <v>82.3</v>
+      </c>
+      <c r="C97" s="3">
+        <v>126.89</v>
+      </c>
+      <c r="D97" s="3">
+        <v>91.26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>9600</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B98" s="3">
+        <v>84.24</v>
+      </c>
+      <c r="C98" s="3">
+        <v>128.29</v>
+      </c>
+      <c r="D98" s="3">
+        <v>93.36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>9700</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B99" s="3">
+        <v>84.24</v>
+      </c>
+      <c r="C99" s="3">
+        <v>128.29</v>
+      </c>
+      <c r="D99" s="3">
+        <v>93.36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>9800</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B100" s="3">
+        <v>84.24</v>
+      </c>
+      <c r="C100" s="3">
+        <v>128.29</v>
+      </c>
+      <c r="D100" s="3">
+        <v>93.36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>9900</v>
       </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B101" s="3">
+        <v>84.24</v>
+      </c>
+      <c r="C101" s="3">
+        <v>128.29</v>
+      </c>
+      <c r="D101" s="3">
+        <v>93.36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>10000</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B102" s="3">
+        <v>86.18</v>
+      </c>
+      <c r="C102" s="3">
+        <v>129.69</v>
+      </c>
+      <c r="D102" s="3">
+        <v>95.45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>10100</v>
       </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B103" s="3">
+        <v>86.18</v>
+      </c>
+      <c r="C103" s="3">
+        <v>129.69</v>
+      </c>
+      <c r="D103" s="3">
+        <v>95.45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>10200</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B104" s="3">
+        <v>86.18</v>
+      </c>
+      <c r="C104" s="3">
+        <v>129.69</v>
+      </c>
+      <c r="D104" s="3">
+        <v>95.45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>10300</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B105" s="3">
+        <v>86.18</v>
+      </c>
+      <c r="C105" s="3">
+        <v>129.69</v>
+      </c>
+      <c r="D105" s="3">
+        <v>95.45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>10400</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B106" s="3">
+        <v>86.18</v>
+      </c>
+      <c r="C106" s="3">
+        <v>129.69</v>
+      </c>
+      <c r="D106" s="3">
+        <v>95.45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>10500</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B107" s="3">
+        <v>88.12</v>
+      </c>
+      <c r="C107" s="3">
+        <v>131.1</v>
+      </c>
+      <c r="D107" s="3">
+        <v>97.52</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>10600</v>
       </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B108" s="3">
+        <v>88.12</v>
+      </c>
+      <c r="C108" s="3">
+        <v>131.1</v>
+      </c>
+      <c r="D108" s="3">
+        <v>97.52</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>10700</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B109" s="3">
+        <v>88.12</v>
+      </c>
+      <c r="C109" s="3">
+        <v>131.1</v>
+      </c>
+      <c r="D109" s="3">
+        <v>97.52</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>10800</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B110" s="3">
+        <v>88.12</v>
+      </c>
+      <c r="C110" s="3">
+        <v>131.1</v>
+      </c>
+      <c r="D110" s="3">
+        <v>97.52</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>10900</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B111" s="3">
+        <v>90.05</v>
+      </c>
+      <c r="C111" s="3">
+        <v>132.54</v>
+      </c>
+      <c r="D111" s="3">
+        <v>99.61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>11000</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B112" s="3">
+        <v>90.05</v>
+      </c>
+      <c r="C112" s="3">
+        <v>132.54</v>
+      </c>
+      <c r="D112" s="3">
+        <v>99.61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>11100</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B113" s="3">
+        <v>90.05</v>
+      </c>
+      <c r="C113" s="3">
+        <v>132.54</v>
+      </c>
+      <c r="D113" s="3">
+        <v>99.61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>11200</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B114" s="3">
+        <v>90.05</v>
+      </c>
+      <c r="C114" s="3">
+        <v>132.54</v>
+      </c>
+      <c r="D114" s="3">
+        <v>99.61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>11300</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B115" s="3">
+        <v>90.05</v>
+      </c>
+      <c r="C115" s="3">
+        <v>132.54</v>
+      </c>
+      <c r="D115" s="3">
+        <v>99.61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>11400</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B116" s="3">
+        <v>96.47</v>
+      </c>
+      <c r="C116" s="3">
+        <v>140.41999999999999</v>
+      </c>
+      <c r="D116" s="3">
+        <v>106.55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>11500</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B117" s="3">
+        <v>96.47</v>
+      </c>
+      <c r="C117" s="3">
+        <v>140.41999999999999</v>
+      </c>
+      <c r="D117" s="3">
+        <v>106.55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>11600</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B118" s="3">
+        <v>96.47</v>
+      </c>
+      <c r="C118" s="3">
+        <v>140.41999999999999</v>
+      </c>
+      <c r="D118" s="3">
+        <v>106.55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>11700</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B119" s="3">
+        <v>96.47</v>
+      </c>
+      <c r="C119" s="3">
+        <v>140.41999999999999</v>
+      </c>
+      <c r="D119" s="3">
+        <v>106.55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>11800</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B120" s="3">
+        <v>98.5</v>
+      </c>
+      <c r="C120" s="3">
+        <v>154.09</v>
+      </c>
+      <c r="D120" s="3">
+        <v>108.74</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>11900</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B121" s="3">
+        <v>98.5</v>
+      </c>
+      <c r="C121" s="3">
+        <v>154.09</v>
+      </c>
+      <c r="D121" s="3">
+        <v>108.74</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>12000</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B122" s="3">
+        <v>98.5</v>
+      </c>
+      <c r="C122" s="3">
+        <v>154.09</v>
+      </c>
+      <c r="D122" s="3">
+        <v>108.74</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>12100</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B123" s="3">
+        <v>98.5</v>
+      </c>
+      <c r="C123" s="3">
+        <v>154.09</v>
+      </c>
+      <c r="D123" s="3">
+        <v>108.74</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>12200</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B124" s="3">
+        <v>98.5</v>
+      </c>
+      <c r="C124" s="3">
+        <v>154.09</v>
+      </c>
+      <c r="D124" s="3">
+        <v>108.74</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>12300</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B125" s="3">
+        <v>100.53</v>
+      </c>
+      <c r="C125" s="3">
+        <v>158.38</v>
+      </c>
+      <c r="D125" s="3">
+        <v>110.93</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>12400</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B126" s="3">
+        <v>100.53</v>
+      </c>
+      <c r="C126" s="3">
+        <v>158.38</v>
+      </c>
+      <c r="D126" s="3">
+        <v>110.93</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>12500</v>
       </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B127" s="3">
+        <v>100.53</v>
+      </c>
+      <c r="C127" s="3">
+        <v>158.38</v>
+      </c>
+      <c r="D127" s="3">
+        <v>110.93</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>12600</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B128" s="3">
+        <v>100.53</v>
+      </c>
+      <c r="C128" s="3">
+        <v>158.38</v>
+      </c>
+      <c r="D128" s="3">
+        <v>110.93</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>12700</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B129" s="3">
+        <v>100.53</v>
+      </c>
+      <c r="C129" s="3">
+        <v>158.38</v>
+      </c>
+      <c r="D129" s="3">
+        <v>110.93</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>12800</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B130" s="3">
+        <v>102.55</v>
+      </c>
+      <c r="C130" s="3">
+        <v>160.06</v>
+      </c>
+      <c r="D130" s="3">
+        <v>113.11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>12900</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B131" s="3">
+        <v>102.55</v>
+      </c>
+      <c r="C131" s="3">
+        <v>160.06</v>
+      </c>
+      <c r="D131" s="3">
+        <v>113.11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>13000</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B132" s="3">
+        <v>102.55</v>
+      </c>
+      <c r="C132" s="3">
+        <v>160.06</v>
+      </c>
+      <c r="D132" s="3">
+        <v>113.11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>13100</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B133" s="3">
+        <v>102.55</v>
+      </c>
+      <c r="C133" s="3">
+        <v>160.06</v>
+      </c>
+      <c r="D133" s="3">
+        <v>113.11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>13200</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B134" s="3">
+        <v>104.59</v>
+      </c>
+      <c r="C134" s="3">
+        <v>165.79</v>
+      </c>
+      <c r="D134" s="3">
+        <v>115.32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>13300</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B135" s="3">
+        <v>104.59</v>
+      </c>
+      <c r="C135" s="3">
+        <v>165.79</v>
+      </c>
+      <c r="D135" s="3">
+        <v>115.32</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>13400</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B136" s="3">
+        <v>104.59</v>
+      </c>
+      <c r="C136" s="3">
+        <v>165.79</v>
+      </c>
+      <c r="D136" s="3">
+        <v>115.32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>13500</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B137" s="3">
+        <v>104.59</v>
+      </c>
+      <c r="C137" s="3">
+        <v>165.79</v>
+      </c>
+      <c r="D137" s="3">
+        <v>115.32</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>13600</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B138" s="3">
+        <v>104.59</v>
+      </c>
+      <c r="C138" s="3">
+        <v>165.79</v>
+      </c>
+      <c r="D138" s="3">
+        <v>115.32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>13700</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B139" s="3">
+        <v>112.6</v>
+      </c>
+      <c r="C139" s="3">
+        <v>180.79</v>
+      </c>
+      <c r="D139" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>13800</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B140" s="3">
+        <v>112.6</v>
+      </c>
+      <c r="C140" s="3">
+        <v>180.79</v>
+      </c>
+      <c r="D140" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>13900</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B141" s="3">
+        <v>112.6</v>
+      </c>
+      <c r="C141" s="3">
+        <v>180.79</v>
+      </c>
+      <c r="D141" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>14000</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B142" s="3">
+        <v>112.6</v>
+      </c>
+      <c r="C142" s="3">
+        <v>180.79</v>
+      </c>
+      <c r="D142" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>14100</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B143" s="3">
+        <v>114.19</v>
+      </c>
+      <c r="C143" s="3">
+        <v>182.8</v>
+      </c>
+      <c r="D143" s="3">
+        <v>125.66</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>14200</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B144" s="3">
+        <v>114.19</v>
+      </c>
+      <c r="C144" s="3">
+        <v>182.8</v>
+      </c>
+      <c r="D144" s="3">
+        <v>125.66</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>14300</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B145" s="3">
+        <v>114.19</v>
+      </c>
+      <c r="C145" s="3">
+        <v>182.8</v>
+      </c>
+      <c r="D145" s="3">
+        <v>125.66</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>14400</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B146" s="3">
+        <v>114.19</v>
+      </c>
+      <c r="C146" s="3">
+        <v>182.8</v>
+      </c>
+      <c r="D146" s="3">
+        <v>125.66</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>14500</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B147" s="3">
+        <v>114.19</v>
+      </c>
+      <c r="C147" s="3">
+        <v>182.8</v>
+      </c>
+      <c r="D147" s="3">
+        <v>125.66</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>14600</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B148" s="3">
+        <v>116.33</v>
+      </c>
+      <c r="C148" s="3">
+        <v>190.45</v>
+      </c>
+      <c r="D148" s="3">
+        <v>127.97</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>14700</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B149" s="3">
+        <v>116.33</v>
+      </c>
+      <c r="C149" s="3">
+        <v>190.45</v>
+      </c>
+      <c r="D149" s="3">
+        <v>127.97</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>14800</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B150" s="3">
+        <v>116.33</v>
+      </c>
+      <c r="C150" s="3">
+        <v>190.45</v>
+      </c>
+      <c r="D150" s="3">
+        <v>127.97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>14900</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B151" s="3">
+        <v>116.33</v>
+      </c>
+      <c r="C151" s="3">
+        <v>190.45</v>
+      </c>
+      <c r="D151" s="3">
+        <v>127.97</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>15000</v>
+      </c>
+      <c r="B152" s="3">
+        <v>118.42</v>
+      </c>
+      <c r="C152" s="3">
+        <v>192.57</v>
+      </c>
+      <c r="D152" s="3">
+        <v>130.25</v>
       </c>
     </row>
   </sheetData>
